--- a/artfynd/A 56700-2025 artfynd.xlsx
+++ b/artfynd/A 56700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,220 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132540298</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57359</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kindbäcksmåla, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>545757</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6263812</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gullabo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Robert Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Robert Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132540329</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57253</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kindbäcksmåla, 52700, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>545757</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6263811</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gullabo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Robert Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Robert Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56700-2025 artfynd.xlsx
+++ b/artfynd/A 56700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132441624</v>
       </c>
       <c r="B2" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>132540298</v>
       </c>
       <c r="B3" t="n">
-        <v>57359</v>
+        <v>57360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>132540329</v>
       </c>
       <c r="B4" t="n">
-        <v>57253</v>
+        <v>57254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56700-2025 artfynd.xlsx
+++ b/artfynd/A 56700-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132441624</v>
       </c>
       <c r="B2" t="n">
-        <v>58323</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>132540298</v>
       </c>
       <c r="B3" t="n">
-        <v>57360</v>
+        <v>57364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>132540329</v>
       </c>
       <c r="B4" t="n">
-        <v>57254</v>
+        <v>57258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56700-2025 artfynd.xlsx
+++ b/artfynd/A 56700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132441624</v>
+        <v>132445068</v>
       </c>
       <c r="B2" t="n">
-        <v>58332</v>
+        <v>90866</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>655</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kindbäcksmåla, Sm</t>
+          <t>Kindbäcksmåla.1, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545757</v>
+        <v>545607</v>
       </c>
       <c r="R2" t="n">
-        <v>6263812</v>
+        <v>6263714</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132540298</v>
+        <v>132876683</v>
       </c>
       <c r="B3" t="n">
-        <v>57369</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -810,20 +810,39 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kindbäcksmåla, Sm</t>
+          <t>Kindbäcksmåla.1 talltitan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545757</v>
+        <v>545583</v>
       </c>
       <c r="R3" t="n">
-        <v>6263812</v>
+        <v>6263727</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +866,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>20:39</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>20:39</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +901,7 @@
         <v>132540329</v>
       </c>
       <c r="B4" t="n">
-        <v>57263</v>
+        <v>57280</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132876683</v>
+        <v>132540298</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,16 +1016,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1024,39 +1033,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kindbäcksmåla.1 talltitan, Sm</t>
+          <t>Kindbäcksmåla, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545583</v>
+        <v>545757</v>
       </c>
       <c r="R5" t="n">
-        <v>6263727</v>
+        <v>6263812</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,12 +1070,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,58 +1112,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132876666</v>
+        <v>132441624</v>
       </c>
       <c r="B6" t="n">
-        <v>58119</v>
+        <v>58349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kindbäcksmåla.1 talltitan, Sm</t>
+          <t>Kindbäcksmåla, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545583</v>
+        <v>545757</v>
       </c>
       <c r="R6" t="n">
-        <v>6263727</v>
+        <v>6263812</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1187,12 +1177,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,6 +1216,220 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132443241</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kindbäcksmåla.1, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>545607</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6263714</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gullabo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Robert Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Robert Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132876666</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kindbäcksmåla.1 talltitan, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>545583</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6263727</v>
+      </c>
+      <c r="S8" t="n">
+        <v>30</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gullabo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Robert Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Robert Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
